--- a/Helix_Demo_Expanded.xlsx
+++ b/Helix_Demo_Expanded.xlsx
@@ -337,10 +337,10 @@
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
-    <col width="92.4" min="1" max="1" bestFit="1" customWidth="1"/>
+    <col width="96.80000000000001" min="1" max="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -361,7 +361,7 @@
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t>5 customers (USD/EUR/USD/JPY/GBP), 5 SKUs, 1 vendor, 2 POs.</t>
+          <t>6 customers (USD/EUR/USD/JPY/GBP/SGD), 5 SKUs, 1 vendor, 2 POs.</t>
         </is>
       </c>
     </row>
@@ -376,28 +376,57 @@
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t>Targets for period_end=2026-03-31:</t>
+          <t>Skip paths exercised by this dataset:</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t>  AR    $1,042.50  (5 customers, 2 flagged)</t>
+          <t>  AR — CUS-1006 has events in prior period only; no Mar 29-31 events → no accrual.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t>  AP    $150,000.00 (2 GR-not-invoiced)</t>
+          <t>  AP — GR-2026-0042 fully covered by INV-V001 → handler skips.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t>  Total $151,042.50</t>
+          <t>  AP — GR-2026-0043 partially covered by INV-V002 → accrues remainder ($30K of $50K).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t>Targets for period_end=2026-03-31:</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t>  AR    $1,042.50  (5 of 6 customers, 2 flagged)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t>  AP    $30,000.00 (1 GR partially uninvoiced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t>  Total $31,042.50</t>
         </is>
       </c>
     </row>
@@ -544,12 +573,12 @@
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="18.700000000000003" min="1" max="1" bestFit="1" customWidth="1"/>
-    <col width="13.200000000000001" min="2" max="2" bestFit="1" customWidth="1"/>
-    <col width="13.200000000000001" min="3" max="3" bestFit="1" customWidth="1"/>
+    <col width="15.400000000000002" min="2" max="2" bestFit="1" customWidth="1"/>
+    <col width="16.5" min="3" max="3" bestFit="1" customWidth="1"/>
     <col width="16.5" min="4" max="4" bestFit="1" customWidth="1"/>
     <col width="16.5" min="5" max="5" bestFit="1" customWidth="1"/>
     <col width="9.9" min="6" max="6" bestFit="1" customWidth="1"/>
@@ -584,6 +613,66 @@
       <c r="F1" s="0" t="inlineStr">
         <is>
           <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>INV-V001</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>VEN-DELL-01</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>PO-2026-0188</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>INV-V002</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>VEN-DELL-01</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>PO-2026-0190</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>20000.0</v>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>posted</t>
         </is>
       </c>
     </row>
@@ -601,11 +690,11 @@
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="15.400000000000002" min="1" max="1" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="2" max="2" bestFit="1" customWidth="1"/>
+    <col width="30.800000000000004" min="2" max="2" bestFit="1" customWidth="1"/>
     <col width="12.100000000000001" min="3" max="3" bestFit="1" customWidth="1"/>
     <col width="11.0" min="4" max="4" bestFit="1" customWidth="1"/>
     <col width="11.0" min="5" max="5" bestFit="1" customWidth="1"/>
@@ -801,6 +890,38 @@
       <c r="F6" s="0" t="inlineStr">
         <is>
           <t>2025-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>CUS-1006</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>Singapore Capital Markets</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F7" s="0" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
         </is>
       </c>
     </row>
@@ -963,7 +1084,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="13.200000000000001" min="1" max="1" bestFit="1" customWidth="1"/>
@@ -1647,6 +1768,31 @@
       <c r="E27" s="0" t="inlineStr">
         <is>
           <t>2026-03-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="inlineStr">
+        <is>
+          <t>evt_h0008</t>
+        </is>
+      </c>
+      <c r="B28" s="0" t="inlineStr">
+        <is>
+          <t>CUS-1006</t>
+        </is>
+      </c>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t>INFERENCE-1K-TOKENS</t>
+        </is>
+      </c>
+      <c r="D28" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1810,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="17.6" min="1" max="1" bestFit="1" customWidth="1"/>
@@ -1907,6 +2053,44 @@
       </c>
       <c r="H6" s="0" t="n">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>INV-2026-0296</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>CUS-1006</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>2026-03-29T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="G7" s="0" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+      <c r="H7" s="0" t="n">
+        <v>0.74</v>
       </c>
     </row>
   </sheetData>
